--- a/AAII_Financials/Quarterly/EQX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EQX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="92">
   <si>
     <t>EQX</t>
   </si>
@@ -656,416 +656,429 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>769800</v>
+      </c>
+      <c r="E8" s="3">
         <v>861600</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>819000</v>
       </c>
-      <c r="G8" s="3">
-        <v>478600</v>
-      </c>
       <c r="H8" s="3">
+        <v>285800</v>
+      </c>
+      <c r="I8" s="3">
         <v>265700</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>428400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>269400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>241300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>297800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>284700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>271600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>234100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>352300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>245100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>224600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>223200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>381200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>245100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>312800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>305900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>255500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>244500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>215400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>130000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>119000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>91900</v>
-      </c>
-      <c r="AE8" s="3">
-        <v>35400</v>
       </c>
       <c r="AF8" s="3">
         <v>35400</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3">
+        <v>35400</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>364000</v>
+      </c>
+      <c r="E9" s="3">
         <v>331700</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>399600</v>
       </c>
-      <c r="G9" s="3">
-        <v>264900</v>
-      </c>
       <c r="H9" s="3">
+        <v>156800</v>
+      </c>
+      <c r="I9" s="3">
         <v>206000</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>268300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>204000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>183800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>198200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>201100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>193000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>173300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>228500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>188800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>170700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>152400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>215500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>152700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>193800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>195800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>114100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>119700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>113000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>76500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>61100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>46100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>24000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>24100</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>405800</v>
+      </c>
+      <c r="E10" s="3">
         <v>529900</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>419400</v>
       </c>
-      <c r="G10" s="3">
-        <v>213700</v>
-      </c>
       <c r="H10" s="3">
+        <v>129000</v>
+      </c>
+      <c r="I10" s="3">
         <v>59700</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>160000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>65400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>57600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>99600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>83600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>78600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>60800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>123700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>56300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>53900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>70900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>165700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>92400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>119000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>110100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>141400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>124800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>102400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>53500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>57900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>45800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>11400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1111,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1142,56 +1156,59 @@
       <c r="P12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q12" s="3">
-        <v>6200</v>
+      <c r="Q12" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="R12" s="3">
         <v>6200</v>
       </c>
       <c r="S12" s="3">
+        <v>6200</v>
+      </c>
+      <c r="T12" s="3">
         <v>4500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>3200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>2900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>5600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>13100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>7900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>4800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>5700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>3900</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>5300</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1700</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>900</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>9200</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1282,192 +1299,201 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-28600</v>
+      </c>
+      <c r="E14" s="3">
         <v>4100</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="F14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3300</v>
       </c>
-      <c r="G14" s="3">
-        <v>14800</v>
-      </c>
       <c r="H14" s="3">
+        <v>17800</v>
+      </c>
+      <c r="I14" s="3">
         <v>15000</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>9900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-579100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1100</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>24</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-29000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-5000</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-80900</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>-172800</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>3200</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>3900</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>16900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>600</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>200</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>13900</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>126500</v>
+      </c>
+      <c r="E15" s="3">
         <v>111900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>119700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>167000</v>
       </c>
-      <c r="G15" s="3">
-        <v>89200</v>
-      </c>
       <c r="H15" s="3">
+        <v>52700</v>
+      </c>
+      <c r="I15" s="3">
         <v>50800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>51000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>58700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>44200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>46200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>61000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>58400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>48200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>47400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>80400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>49100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>37300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>42600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>74400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>43700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>62800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>51700</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>43800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>36300</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>35400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>17100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>19700</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>11300</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>3900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1523,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>522400</v>
+      </c>
+      <c r="E17" s="3">
         <v>471400</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="F17" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>613800</v>
       </c>
-      <c r="G17" s="3">
-        <v>374800</v>
-      </c>
       <c r="H17" s="3">
+        <v>235800</v>
+      </c>
+      <c r="I17" s="3">
         <v>274900</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>344200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>263500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>246600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>272500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>276100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>257500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>232500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>334200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>252800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>228000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>210100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>228600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>220000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>118200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>263400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>205700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>179800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>183300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>103600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>92100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>65600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>34600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>34400</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>247400</v>
+      </c>
+      <c r="E18" s="3">
         <v>390200</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="F18" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>205200</v>
       </c>
-      <c r="G18" s="3">
-        <v>103800</v>
-      </c>
       <c r="H18" s="3">
+        <v>50100</v>
+      </c>
+      <c r="I18" s="3">
         <v>-9200</v>
       </c>
-      <c r="I18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>84200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>25300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>8600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>14100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>18000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-7700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-3400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>13100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>152600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>25100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>194600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>42500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>49800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>64700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>32100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>26400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>26900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>26300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1715,237 +1748,244 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-39100</v>
+      </c>
+      <c r="E20" s="3">
         <v>44700</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="F20" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>39200</v>
       </c>
-      <c r="G20" s="3">
-        <v>-3100</v>
-      </c>
       <c r="H20" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="I20" s="3">
         <v>800</v>
       </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>19700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>15400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>12400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>13100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-24900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-20400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-45900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-29200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>9200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-32900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>341700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>51100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>17400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-51700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-104600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>9000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-32600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-14700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-13500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-7300</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>412900</v>
+      </c>
+      <c r="E21" s="3">
         <v>457500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>119700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>333000</v>
       </c>
-      <c r="G21" s="3">
-        <v>196100</v>
-      </c>
       <c r="H21" s="3">
+        <v>114300</v>
+      </c>
+      <c r="I21" s="3">
         <v>40900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>51000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>123100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>34700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>28600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>84800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>64700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>63700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>35900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>74400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>21100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-12000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>26500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>233900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>36900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>593800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>146600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>121600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>49600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-28400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>52500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>14000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>21800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-8200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E22" s="3">
         <v>31700</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="F22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>50900</v>
       </c>
-      <c r="G22" s="3">
-        <v>45300</v>
-      </c>
       <c r="H22" s="3">
+        <v>43900</v>
+      </c>
+      <c r="I22" s="3">
         <v>46400</v>
       </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>19700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>20700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>17400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>17900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>15300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>14300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>12700</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
@@ -1991,192 +2031,201 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>305600</v>
+      </c>
+      <c r="E23" s="3">
         <v>314000</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="F23" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>115000</v>
       </c>
-      <c r="G23" s="3">
-        <v>49300</v>
-      </c>
       <c r="H23" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I23" s="3">
         <v>-69500</v>
       </c>
-      <c r="I23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>36800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>551300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-34200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>8300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-5900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>7800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-6900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-28000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-49200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-16100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>161800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-7800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>536300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>93600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>67200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>13000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-72500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>35400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-5700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>11600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-12700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-6400</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>87000</v>
+      </c>
+      <c r="E24" s="3">
         <v>126800</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>29400</v>
       </c>
-      <c r="G24" s="3">
-        <v>25500</v>
-      </c>
       <c r="H24" s="3">
+        <v>30700</v>
+      </c>
+      <c r="I24" s="3">
         <v>9000</v>
       </c>
-      <c r="I24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>36500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>197900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>8500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>4500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-8100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-9600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-37500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>29500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-22300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-2500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-21900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>26600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-24000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>9700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>5300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>29800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>3500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2267,192 +2316,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>218600</v>
+      </c>
+      <c r="E26" s="3">
         <v>187200</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="F26" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>85600</v>
       </c>
-      <c r="G26" s="3">
-        <v>23800</v>
-      </c>
       <c r="H26" s="3">
+        <v>-28400</v>
+      </c>
+      <c r="I26" s="3">
         <v>-78500</v>
       </c>
-      <c r="I26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>353500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-42800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>17400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>30700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-30100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-78700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-19800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>184100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-5200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>558200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>67000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>91200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-77800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>5600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-8500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>8100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-11600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-8300</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>230600</v>
+      </c>
+      <c r="E27" s="3">
         <v>310100</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="F27" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>85600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>23800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-75500</v>
       </c>
-      <c r="I27" s="3" t="s">
+      <c r="J27" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>353500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-42800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>17400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>30700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-30100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-78700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-19800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>184100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-5200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>558200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>67000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>91200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-77800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>5600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-8500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>8100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-10500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-7400</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2543,17 +2601,20 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E29" s="3">
         <v>122900</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
       <c r="F29" s="3">
         <v>0</v>
       </c>
@@ -2561,11 +2622,11 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>52300</v>
+      </c>
+      <c r="I29" s="3">
         <v>3000</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
         <v>0</v>
       </c>
@@ -2617,14 +2678,14 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>24</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
+      <c r="AC29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AD29" s="3">
         <v>0</v>
@@ -2635,8 +2696,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2791,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2886,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>39100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-44700</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="F32" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-39200</v>
       </c>
-      <c r="G32" s="3">
-        <v>3100</v>
-      </c>
       <c r="H32" s="3">
+        <v>11500</v>
+      </c>
+      <c r="I32" s="3">
         <v>-800</v>
       </c>
-      <c r="I32" s="3" t="s">
+      <c r="J32" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-19700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-15400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-12400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-13100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>24900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>20400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>45900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>29200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-9200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>32900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-341700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-51100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-17400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>51700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>104600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-9000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>32600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>14700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>13500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>230600</v>
+      </c>
+      <c r="E33" s="3">
         <v>310100</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="F33" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>85600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>23800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-75500</v>
       </c>
-      <c r="I33" s="3" t="s">
+      <c r="J33" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>353500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-42800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>17400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>30700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-30100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-78700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-19800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>184100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-5200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>558200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>67000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>91200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-77800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>5600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-8500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>8100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-10500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-7400</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3171,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>230600</v>
+      </c>
+      <c r="E35" s="3">
         <v>310100</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="F35" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>85600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>23800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-75500</v>
       </c>
-      <c r="I35" s="3" t="s">
+      <c r="J35" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>353500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-42800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>17400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>30700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-30100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-78700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-19800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>184100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-5200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>558200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>67000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>91200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-77800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>5600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-8500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>8100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-10500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-7400</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3403,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,165 +3438,169 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>317800</v>
+      </c>
+      <c r="E41" s="3">
         <v>363000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>407400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>348500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>406700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>172900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>239300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>167800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>167500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>125300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>192000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>356700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>174400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>284900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>272700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>141900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>159700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>151200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>305500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>300300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>461700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>422900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>344900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>310700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>494100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>303100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>67700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>45500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>33000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>163800</v>
+      </c>
+      <c r="E42" s="3">
         <v>136700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>162700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>54800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>23800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>5400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>6100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>6900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>6300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>71300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>92700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>80700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>122600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>133900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>50100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>70000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>97700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>177400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>240500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>159600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>248900</v>
-      </c>
-      <c r="X42" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="Y42" s="3" t="s">
         <v>24</v>
@@ -3524,204 +3614,213 @@
       <c r="AB42" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AC42" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD42" s="3">
         <v>1000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1200</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1600</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>74500</v>
+      </c>
+      <c r="E43" s="3">
         <v>61100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>65500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>133900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>83200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>127600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>70000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>64500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>63100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>65500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>82300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>75800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>63000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>78200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>103400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>79500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>96800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>46000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>50300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>66300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>114500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>62800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>55900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>47200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>40200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>58100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>31800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>30400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>21500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>21700</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>435700</v>
+      </c>
+      <c r="E44" s="3">
         <v>392000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>369800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>541000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>439400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>244100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>417500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>440800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>418900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>414600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>412000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>347900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>333900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>309000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>360100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>225500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>220000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>214900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>201600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>202400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>279100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>261100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>208300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>214900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>150800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>143100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>46300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>57300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>57800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>54900</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3729,82 +3828,82 @@
         <v>2000</v>
       </c>
       <c r="E45" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F45" s="3">
         <v>936900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>179100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>13900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>17700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>19700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>32900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>20700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>103600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>75100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>101000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>360400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>365300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>31100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>53000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>187400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>36900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>24600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>29000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>17800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1900</v>
-      </c>
-      <c r="AD45" s="3">
-        <v>600</v>
       </c>
       <c r="AE45" s="3">
         <v>600</v>
@@ -3812,100 +3911,106 @@
       <c r="AF45" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1029600</v>
+      </c>
+      <c r="E46" s="3">
         <v>988300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1970600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1293100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1015800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>592800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>784100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>727200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>711300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>712500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>834000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>911100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>767800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>859300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>889900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>592100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>675200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>949800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1163200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>759700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1157200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>934200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>646000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>597400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>714000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>522000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>148700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>134900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>114600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>103100</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3915,181 +4020,187 @@
       <c r="E47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G47" s="3">
         <v>55100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>26600</v>
       </c>
-      <c r="H47" s="3" t="s">
+      <c r="I47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>32300</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M47" s="3">
         <v>28100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>29300</v>
-      </c>
-      <c r="N47" s="3">
-        <v>29700</v>
       </c>
       <c r="O47" s="3">
         <v>29700</v>
       </c>
       <c r="P47" s="3">
+        <v>29700</v>
+      </c>
+      <c r="Q47" s="3">
         <v>33000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>204900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>154400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>149500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>123700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>125300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>180600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>272400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>21200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>22300</v>
       </c>
-      <c r="Z47" s="3" t="s">
+      <c r="AA47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>10100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>6200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>7200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>5400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>5700</v>
       </c>
-      <c r="AF47" s="3" t="s">
+      <c r="AG47" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7984400</v>
+      </c>
+      <c r="E48" s="3">
         <v>7948800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7910300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>8443000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>8419200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5560200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5564700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5714600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5581000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3274300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3225200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3077500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3026700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2939800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3858800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2740000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2654900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2577300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2497900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2562500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3488200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2542900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1858700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1855400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1903200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1892300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>511700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>499200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>557200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>565100</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4180,8 +4291,11 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4386,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4481,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>780800</v>
+      </c>
+      <c r="E52" s="3">
         <v>718900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>635800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>462100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>518100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>448000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>301000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>328900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>326600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>249100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>236700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>252900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>215900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>196800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>285200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>197800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>210900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>183800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>180900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>162600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>210600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>179900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>146400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>151600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>166600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>171600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>171800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>152200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>102100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>83700</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4671,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9794800</v>
+      </c>
+      <c r="E54" s="3">
         <v>9656100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10535400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10308300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10020800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6670000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6713600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6838100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6683700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4292900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4350400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4291800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4060000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4029000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5238900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3684300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3690500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3834600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3967400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3665300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5128400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3678200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2673400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2604400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2794000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2592000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>839400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>791700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>779500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>751900</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4803,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,560 +4838,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>325600</v>
+      </c>
+      <c r="E57" s="3">
         <v>331700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>104500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>522900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>442700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>224500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>128500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>275500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>263500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>218400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>112800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>220000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>205000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>213600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>325800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>195100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>171700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>162300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>190100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>156400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>200200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>177100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>130500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>109000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>123500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>115300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>67200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>46500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>41000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>92100</v>
+      </c>
+      <c r="E58" s="3">
         <v>66000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>242700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>221300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>285500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>154900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>171400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>349300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>206800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>296600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>168900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>168400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>145000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>8200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>29100</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
       <c r="S58" s="3">
-        <v>26700</v>
+        <v>0</v>
       </c>
       <c r="T58" s="3">
         <v>26700</v>
       </c>
       <c r="U58" s="3">
+        <v>26700</v>
+      </c>
+      <c r="V58" s="3">
         <v>44800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>44100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>61900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>47700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>22300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>14900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>8200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>27200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>62100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>21400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>40700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>70400</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>354900</v>
+      </c>
+      <c r="E59" s="3">
         <v>396300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>716900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>456300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>355500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>312400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>259300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>235300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>173600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>91200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>70600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>39500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>38900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>14300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>26800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>35000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>145500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>167600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>83800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>107900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>185500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>69900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>78100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>65400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>40300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1600</v>
-      </c>
-      <c r="AE59" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AF59" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>774400</v>
+      </c>
+      <c r="E60" s="3">
         <v>797800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1262000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1204500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1085400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>693900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>689100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>860100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>646600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>611200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>479600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>401100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>389500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>260700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>369100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>221900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>233400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>334400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>402600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>284300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>370000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>410300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>222700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>202100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>197100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>182800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>131900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>69500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>81700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>108400</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>747000</v>
+      </c>
+      <c r="E61" s="3">
         <v>721400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1592600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1717600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1801100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1345000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1358600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1353600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1458000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>708400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>833900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>967900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>717400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>854300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1144000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>725800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>605200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>509600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>541000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>547300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>766400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>738500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>541900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>549900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>752700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>733500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>203300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>242000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>221600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>156500</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>269100</v>
+      </c>
+      <c r="E62" s="3">
         <v>397800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>308500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>317700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>336400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>264000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>201600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>197000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>196700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>146800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>155200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>149300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>152300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>138500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>529100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>432700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>460500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>461500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>438500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>504300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>743000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>527400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>460400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>474600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>478800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>452300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>101000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>70400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>62600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>69100</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5501,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5444,8 +5596,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5691,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3426300</v>
+      </c>
+      <c r="E66" s="3">
         <v>3530800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4740100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4732600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4729100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3346900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3316000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3590500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3468200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1885900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1907900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1916400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1655800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1642500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2042300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1380400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1299100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1305500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1382000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1335900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1879400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1676200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1224900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1226600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1428600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1368500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>436300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>381900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>365800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>350500</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5823,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5916,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6011,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6106,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6201,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1343800</v>
+      </c>
+      <c r="E72" s="3">
         <v>1126600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>820000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>632500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>546900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>523000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>613700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>516100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>515800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>305800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>348500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>344700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>342400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>337100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>501500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>374000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>405100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>468700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>493600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>309500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>433000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-24900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-69500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-136000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-129500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-66000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-102600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-95600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-89800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-90600</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6391,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6486,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6581,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6368500</v>
+      </c>
+      <c r="E76" s="3">
         <v>6125200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5795300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5575700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5291700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3323100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3397600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3247600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3215500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2407000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2442500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2375400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2404300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2386400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3196700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2303900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2391400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2529100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2585300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2329500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3249100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2002000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1448500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1377700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1365400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1223500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>403100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>409800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>413700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>401400</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6771,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>230600</v>
+      </c>
+      <c r="E81" s="3">
         <v>310100</v>
       </c>
-      <c r="E81" s="3" t="s">
+      <c r="F81" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>85600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>23800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-75500</v>
       </c>
-      <c r="I81" s="3" t="s">
+      <c r="J81" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>353500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-42800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>17400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>30700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-30100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-78700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-19800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>184100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-5200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>558200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>67000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>91200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-77800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>5600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-8500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>8100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-10500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-7400</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,100 +7003,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>59100</v>
+      </c>
+      <c r="E83" s="3">
         <v>97600</v>
       </c>
-      <c r="E83" s="3" t="s">
+      <c r="F83" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>59300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>44400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>46400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>61300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>58900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>48400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>47500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>59800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>49100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>37300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>42600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>81300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>49100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>37300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>42600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>72100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>44600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>57500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>53000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>54300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>36600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>43800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>17400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>19700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>10200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>4500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7191,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7286,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7381,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7476,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7571,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>203400</v>
+      </c>
+      <c r="E89" s="3">
         <v>236800</v>
       </c>
-      <c r="E89" s="3" t="s">
+      <c r="F89" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>240800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>132900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>54500</v>
       </c>
-      <c r="I89" s="3" t="s">
+      <c r="J89" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>139500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-33000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>17900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>125900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>69300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>19900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>143400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>61900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>54200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-26900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-16400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>155400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>64800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>29400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>105700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>90100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>68600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>93600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>3500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>38900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>38000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-12100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7703,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-204800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-184800</v>
       </c>
-      <c r="E91" s="3" t="s">
+      <c r="F91" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-235500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-96000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-93800</v>
       </c>
-      <c r="I91" s="3" t="s">
+      <c r="J91" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-124400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-88400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-104800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-137000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-147600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-110900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-127900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-139500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-151500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-142200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-123900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-107400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-71500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-130500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-94400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-50900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-47700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-39900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-34400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-15800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-71100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-6100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7891,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7986,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-206500</v>
+      </c>
+      <c r="E94" s="3">
         <v>709000</v>
       </c>
-      <c r="E94" s="3" t="s">
+      <c r="F94" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-234600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>96900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-133500</v>
       </c>
-      <c r="I94" s="3" t="s">
+      <c r="J94" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-125900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-745400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-108800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-143500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-150800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-111600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-56800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-115400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-151700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-57600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-124800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-126000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-73600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-80700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-119400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-61700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-45200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-43200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>20800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-15700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-25400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-24500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-45700</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,16 +8118,17 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
         <v>11800</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>24</v>
+      <c r="E96" s="3">
+        <v>11800</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>24</v>
@@ -7929,8 +8163,8 @@
       <c r="P96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -7977,8 +8211,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8306,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8401,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,280 +8496,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-44500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1010400</v>
       </c>
-      <c r="E100" s="3" t="s">
+      <c r="F100" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-53000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>10400</v>
       </c>
-      <c r="I100" s="3" t="s">
+      <c r="J100" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-13700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>822600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>24900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-148500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>264600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-20100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>132300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>82000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>82400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-7600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-20200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-18500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>64000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-12200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>7500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-196000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>150100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>228500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>45500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>12900</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E101" s="3">
         <v>2100</v>
       </c>
-      <c r="E101" s="3" t="s">
+      <c r="F101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-2000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-4100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>4500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-2300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-4100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>4500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-6300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>6100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-6900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>5500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-3500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-45200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-67000</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-47000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>233800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-66400</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>42200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-66700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-164700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>182300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-110500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>84100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>80000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-17800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-6100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-144300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>9800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-33600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>18800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-32800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>34200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-183300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>191000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>235300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>22200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>12400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>9000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-36800</v>
       </c>
     </row>
